--- a/conditions/training.xlsx
+++ b/conditions/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrikhrabanek/Documents/Programming/creaky_experiment/conditions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pahr0811/Documents/PhD/Year_1/Study_1/PsychoPy_experiment/creaky_experiment/conditions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54067BC6-D588-BB41-AE29-BACC01DDBA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECA214F-6C0E-9F41-8A0D-3583CA11E2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="29040" windowHeight="17640" xr2:uid="{E94A0D02-C4AD-45DA-9BE1-25E231290689}"/>
+    <workbookView xWindow="53620" yWindow="5200" windowWidth="29040" windowHeight="17640" xr2:uid="{E94A0D02-C4AD-45DA-9BE1-25E231290689}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t>stimType</t>
   </si>
@@ -57,12 +57,6 @@
   </si>
   <si>
     <t>training_stimuli/hun_creaky.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/hun_modal.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/jap_modal.wav</t>
   </si>
   <si>
     <t>training_stimuli/jap_creaky.wav</t>
@@ -754,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FA11AE-AFD2-454A-A1FD-CF62DB163988}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.3984375" bestFit="1" customWidth="1"/>
@@ -762,7 +756,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -813,7 +807,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -834,7 +828,7 @@
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -843,7 +837,7 @@
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -852,10 +846,10 @@
     </row>
     <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -864,7 +858,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" s="2"/>
     </row>
@@ -887,21 +881,7 @@
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
       <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -910,26 +890,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="805e3853-2971-4830-a200-7929f1998a0d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1abb6105-976e-4641-94d5-932be0f0089d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100281F5302C0C8424184A8BFB4F64AD156" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a7dddae9028d61b06595b7475003a62f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="805e3853-2971-4830-a200-7929f1998a0d" xmlns:ns3="1abb6105-976e-4641-94d5-932be0f0089d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd95256a0d3ea48f6d8d5ce446b80fb5" ns2:_="" ns3:_="">
     <xsd:import namespace="805e3853-2971-4830-a200-7929f1998a0d"/>
@@ -1118,10 +1078,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="805e3853-2971-4830-a200-7929f1998a0d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1abb6105-976e-4641-94d5-932be0f0089d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C198A863-1F77-4B90-9B7E-D9A5CE4D14B1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E047D9-D247-4E2D-8E73-39594A3DD58C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="805e3853-2971-4830-a200-7929f1998a0d"/>
+    <ds:schemaRef ds:uri="1abb6105-976e-4641-94d5-932be0f0089d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1140,20 +1131,15 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E047D9-D247-4E2D-8E73-39594A3DD58C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C198A863-1F77-4B90-9B7E-D9A5CE4D14B1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="805e3853-2971-4830-a200-7929f1998a0d"/>
-    <ds:schemaRef ds:uri="1abb6105-976e-4641-94d5-932be0f0089d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{35b66c34-d3f7-4b74-a2f5-5e46d77d2b05}" enabled="1" method="Privileged" siteId="{1e586649-7317-42fb-8949-66923d34ba7e}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>